--- a/naver-place-crawler/results_health/연수구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/연수구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>머슬몽키짐</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>coke3183@naver.com</t>
+          <t>fitnessinssongdo@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1407-9979</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muscle_monkey_gym</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>234</v>
+        <v>1572</v>
       </c>
       <c r="Q2" t="n">
-        <v>147</v>
+        <v>731</v>
       </c>
       <c r="R2" t="n">
-        <v>381</v>
+        <v>2303</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>38234040</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38234040</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>카이짐동춘점 헬스PT</t>
+          <t>연수동PT 하이엔드 연수점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kaigym2@naver.com</t>
+          <t>highendfit@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1327-0169</t>
+          <t>0507-1466-3414</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로 260 3층 304~313호</t>
+          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kaigym2</t>
+          <t>http://www.highendfitness.kr/default/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48</v>
+        <v>699</v>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="R3" t="n">
-        <v>123</v>
+        <v>1008</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2079653679</t>
+          <t>1725784787</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079653679</t>
+          <t>https://m.place.naver.com/place/1725784787</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>연수동PT 하이엔드 연수점</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>highendfit@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1466-3414</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.highendfitness.kr/default/</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -800,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>693</v>
+        <v>115</v>
       </c>
       <c r="Q4" t="n">
-        <v>308</v>
+        <v>644</v>
       </c>
       <c r="R4" t="n">
-        <v>1001</v>
+        <v>759</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1725784787</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725784787</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
+          <t>카이짐동춘점 헬스PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>from-body@naver.com</t>
+          <t>kaigym2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1425-0923</t>
+          <t>0507-1327-0169</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
+          <t>인천광역시 연수구 앵고개로 260 3층 304~313호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://frombody.kr</t>
+          <t>https://blog.naver.com/kaigym2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1538</v>
+        <v>89</v>
       </c>
       <c r="R5" t="n">
-        <v>1829</v>
+        <v>145</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +918,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1472986584</t>
+          <t>2079653679</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472986584</t>
+          <t>https://m.place.naver.com/place/2079653679</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>영스짐 헬스&amp;PT&amp;GX 옥련점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>young-gym-oy@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1369-4733</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 독배로 35 601, 602호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://blog.naver.com/young-gym-oy</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>315</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>1808</v>
+        <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>2123</v>
+        <v>84</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>2030292479</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/2030292479</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피지컬랩 송도PT</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>maxyh7@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1332-2194</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고 타워 502호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maxyh7/222056811037</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>183</v>
+        <v>1386</v>
       </c>
       <c r="Q7" t="n">
-        <v>546</v>
+        <v>933</v>
       </c>
       <c r="R7" t="n">
-        <v>729</v>
+        <v>2319</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1826127652</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1826127652</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1355</v>
+        <v>317</v>
       </c>
       <c r="Q8" t="n">
-        <v>920</v>
+        <v>1924</v>
       </c>
       <c r="R8" t="n">
-        <v>2275</v>
+        <v>2241</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q9" t="n">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="R9" t="n">
-        <v>500</v>
+        <v>591</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,105 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FWC스포츠센터</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>fwcsports@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1360-7005</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>http://www.fwcsongdo.com/</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>208</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>643</v>
-      </c>
-      <c r="R10" t="n">
-        <v>851</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>34249321</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/34249321</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/연수구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/연수구_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="Q2" t="n">
         <v>731</v>
       </c>
       <c r="R2" t="n">
-        <v>2303</v>
+        <v>2309</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>무포스 PT FT 송도점</t>
+          <t>올피플 24시 헬스 PT 연수 동춘점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>moveforstrength@naver.com</t>
+          <t>all_people@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1406-4500</t>
+          <t>0507-1400-8338</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.moveforstrength.co.kr/</t>
+          <t>http://pf.kakao.com/_gAxafn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>115</v>
+        <v>477</v>
       </c>
       <c r="Q4" t="n">
-        <v>644</v>
+        <v>1195</v>
       </c>
       <c r="R4" t="n">
-        <v>759</v>
+        <v>1672</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1426191152</t>
+          <t>1253864345</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426191152</t>
+          <t>https://m.place.naver.com/place/1253864345</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,39 +846,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>카이짐동춘점 헬스PT</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kaigym2@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1327-0169</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로 260 3층 304~313호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kaigym2</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>89</v>
+        <v>644</v>
       </c>
       <c r="R5" t="n">
-        <v>145</v>
+        <v>759</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2079653679</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079653679</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1188,10 +1188,10 @@
         <v>317</v>
       </c>
       <c r="Q8" t="n">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="R8" t="n">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1222,52 +1222,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
+          <t>FWC스포츠센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>physiostudio_7@naver.com</t>
+          <t>fwcsports@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1356-5739</t>
+          <t>0507-1360-7005</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physiostudio_7</t>
+          <t>http://www.fwcsongdo.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qg2m</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="n">
-        <v>538</v>
+        <v>643</v>
       </c>
       <c r="R9" t="n">
-        <v>591</v>
+        <v>851</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2019067639</t>
+          <t>34249321</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019067639</t>
+          <t>https://m.place.naver.com/place/34249321</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/연수구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/연수구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>머슬몽키짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessinssongdo@naver.com</t>
+          <t>coke3183@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1407-9979</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://www.instagram.com/muscle_monkey_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1578</v>
+        <v>234</v>
       </c>
       <c r="Q2" t="n">
-        <v>731</v>
+        <v>147</v>
       </c>
       <c r="R2" t="n">
-        <v>2309</v>
+        <v>381</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>38234040</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/38234040</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>연수동PT 하이엔드 연수점</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>highendfit@naver.com</t>
+          <t>fitnessinssongdo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1466-3414</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.highendfitness.kr/default/</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>699</v>
+        <v>1578</v>
       </c>
       <c r="Q3" t="n">
-        <v>309</v>
+        <v>731</v>
       </c>
       <c r="R3" t="n">
-        <v>1008</v>
+        <v>2309</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1725784787</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725784787</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>올피플 24시 헬스 PT 연수 동춘점</t>
+          <t>연수동PT 하이엔드 연수점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>all_people@naver.com</t>
+          <t>highendfit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1400-8338</t>
+          <t>0507-1466-3414</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
+          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gAxafn</t>
+          <t>http://www.highendfitness.kr/default/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>477</v>
+        <v>699</v>
       </c>
       <c r="Q4" t="n">
-        <v>1195</v>
+        <v>309</v>
       </c>
       <c r="R4" t="n">
-        <v>1672</v>
+        <v>1008</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1253864345</t>
+          <t>1725784787</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253864345</t>
+          <t>https://m.place.naver.com/place/1725784787</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>무포스 PT FT 송도점</t>
+          <t>올피플 24시 헬스 PT 연수 동춘점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>moveforstrength@naver.com</t>
+          <t>all_people@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1406-4500</t>
+          <t>0507-1400-8338</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.moveforstrength.co.kr/</t>
+          <t>http://pf.kakao.com/_gAxafn</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>115</v>
+        <v>477</v>
       </c>
       <c r="Q5" t="n">
-        <v>644</v>
+        <v>1195</v>
       </c>
       <c r="R5" t="n">
-        <v>759</v>
+        <v>1672</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1426191152</t>
+          <t>1253864345</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426191152</t>
+          <t>https://m.place.naver.com/place/1253864345</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1000,10 +1000,10 @@
         <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="Q7" t="n">
         <v>933</v>
       </c>
       <c r="R7" t="n">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>317</v>
       </c>
       <c r="Q8" t="n">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="R8" t="n">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1307,6 +1307,100 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>코어앤모어 PT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>coreandmore@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1319-5328</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>111</v>
+      </c>
+      <c r="R10" t="n">
+        <v>191</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2021439008</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021439008</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/연수구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/연수구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>머슬몽키짐</t>
+          <t>F45 송도</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>coke3183@naver.com</t>
+          <t>f45songdo@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1407-9979</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
+          <t>인천광역시 연수구 인천타워대로 241 부영송도타워 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muscle_monkey_gym</t>
+          <t>https://www.instagram.com/f45_training_songdo/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>234</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="R2" t="n">
-        <v>381</v>
+        <v>66</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>38234040</t>
+          <t>1656342994</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38234040</t>
+          <t>https://m.place.naver.com/place/1656342994</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -658,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>센트럴피티스튜디오 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitnessinssongdo@naver.com</t>
+          <t>trainer_dy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1417-2729</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 센트럴로 232 센1몰 A동 208호~210호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://www.instagram.com/central_pt_studio</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1578</v>
+        <v>151</v>
       </c>
       <c r="Q3" t="n">
-        <v>731</v>
+        <v>673</v>
       </c>
       <c r="R3" t="n">
-        <v>2309</v>
+        <v>824</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>1627643135</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/1627643135</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,34 +748,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>연수동PT 하이엔드 연수점</t>
+          <t>짐작 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>highendfit@naver.com</t>
+          <t>gymzak@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1466-3414</t>
+          <t>0507-1469-0425</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
+          <t>인천광역시 연수구 해돋이로152번길 9 1동 3층 305호,306호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.highendfitness.kr/default/</t>
+          <t>https://blog.naver.com/gymzak</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,22 +796,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>699</v>
+        <v>187</v>
       </c>
       <c r="Q4" t="n">
-        <v>309</v>
+        <v>401</v>
       </c>
       <c r="R4" t="n">
-        <v>1008</v>
+        <v>588</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1725784787</t>
+          <t>1392612926</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725784787</t>
+          <t>https://m.place.naver.com/place/1392612926</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,34 +842,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>올피플 24시 헬스 PT 연수 동춘점</t>
+          <t>스피닝하이</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>all_people@naver.com</t>
+          <t>spinninghigh@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1400-8338</t>
+          <t>0507-1445-3359</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
+          <t>인천광역시 연수구 센트럴로 194 에이동 2층 211호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gAxafn</t>
+          <t>https://www.instagram.com/spinninghigh_official/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>477</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1195</v>
+        <v>59</v>
       </c>
       <c r="R5" t="n">
-        <v>1672</v>
+        <v>73</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1253864345</t>
+          <t>2054788890</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253864345</t>
+          <t>https://m.place.naver.com/place/2054788890</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>영스짐 헬스&amp;PT&amp;GX 옥련점</t>
+          <t>씨제이휘트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>young-gym-oy@naver.com</t>
+          <t>crewjfitness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1369-4733</t>
+          <t>0507-1494-6288</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 독배로 35 601, 602호</t>
+          <t>인천광역시 연수구 앵고개로254번길 19-3 3층 CJ휘트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/young-gym-oy</t>
+          <t>https://blog.naver.com/crewjfitness</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2030292479</t>
+          <t>155034921</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030292479</t>
+          <t>https://m.place.naver.com/place/155034921</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1030,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>뉴젠 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>new-gen@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1375-1998</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 인천타워대로180번길 11 상가 A동 3층 315호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://pf.kakao.com/_xhcfxnxj</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1387</v>
+        <v>406</v>
       </c>
       <c r="Q7" t="n">
-        <v>933</v>
+        <v>1635</v>
       </c>
       <c r="R7" t="n">
-        <v>2320</v>
+        <v>2041</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,61 +1102,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1587802368</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1587802368</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>뉴더블유짐 헬스&amp;PT/재활</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>csys026@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1408-6714</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 한나루로 157 최송빌딩 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>317</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1930</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>2247</v>
+        <v>23</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,78 +1196,74 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1064727013</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1064727013</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>바이블짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>wnsrlf9293@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1484-7902</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천광역시 연수구 학나래로6번길 6 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>https://blog.naver.com/wnsrlf9293</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>208</v>
+        <v>492</v>
       </c>
       <c r="Q9" t="n">
-        <v>643</v>
+        <v>306</v>
       </c>
       <c r="R9" t="n">
-        <v>851</v>
+        <v>798</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>12782122</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/12782122</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>영스짐 헬스&amp;PT&amp;GX 옥련점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>young-gym-oy@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1369-4733</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천광역시 연수구 독배로 35 601, 602호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>https://blog.naver.com/young-gym-oy</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,36 +1365,8848 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30</v>
+      </c>
+      <c r="R10" t="n">
+        <v>89</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2030292479</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030292479</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>연수동PT 하이엔드 연수점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>highendfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1466-3414</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://www.highendfitness.kr/default/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>699</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>308</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1007</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1725784787</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1725784787</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐투투 헬스&amp;PT 송도점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gym22-@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1368-4473</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 69 3층 309호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gym22-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>614</v>
+      </c>
+      <c r="R12" t="n">
+        <v>717</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1692085107</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692085107</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>제로피트니스 24시 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oozt6@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1369-5733</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로188번길 12 이리옴3빌딩 2층 203호 제로피트니스</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/xero.fitness</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>676</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>47</v>
+      </c>
+      <c r="R13" t="n">
+        <v>723</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1195736737</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1195736737</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>메이드핏 송도역점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>madefit3@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1485-9697</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 비류대로 184 태영프라자 7층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/madefit.songdo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>2204</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>376</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2580</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1938015563</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1938015563</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 송도점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fitnessinssongdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1468-2286</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://fitnessinstitute.co.kr/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1578</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>731</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2309</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1806077033</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806077033</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>머슬몽키짐</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>coke3183@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1407-9979</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muscle_monkey_gym</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>147</v>
+      </c>
+      <c r="R16" t="n">
+        <v>381</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>38234040</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38234040</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>송도 크로스핏</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>songdocrossfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1313-2546</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 118 마린프라자 B01호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/songdo.crossfit</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>415</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>372</v>
+      </c>
+      <c r="R17" t="n">
+        <v>787</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>35297464</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35297464</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>라이칸짐 헬스&amp;PT&amp;필라</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lycan100@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1462-3671</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 청능대로 75 6층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lycan.gym24?igsh=MTRjMjh2NGVlZWllOA==</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1097</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2205</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1061751111</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1061751111</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>히든핏 PT&amp;헬스 송도점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hiddenfit__@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1349-9712</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로28번길 50 더샵 송도트리플타워west동 2층 219~221호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hiddenfit__</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>566</v>
+      </c>
+      <c r="R19" t="n">
+        <v>746</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1355031564</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355031564</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>070-4594-4413</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 선학동</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1462839719</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462839719</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>바디채널&amp;바레톤 연수역점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>bodygym15@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1447-2623</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 벚꽃로 106 연수광장프라자 2층, 3층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodychannel__yeonsu/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>474</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2639</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3113</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1852344251</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1852344251</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>팀케이짐</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>yeseoul5@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1401-0285</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 샘말로7번길 13 2층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/TeamKgym</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>379</v>
+      </c>
+      <c r="R22" t="n">
+        <v>391</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>30805607</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30805607</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>에스에이치 IT휘트니스점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>shsongdo84@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1434-8501</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로 32 송도테크노파크IT센터 3층 IT휘트니스</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/shsongdo84</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>718</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1158</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1876</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1206107606</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206107606</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>풀바디짐 헬스&amp;PT 송도점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>byun0124@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1395-0448</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 6층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://instagram.com/kimjunkyung9696</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>421</v>
+      </c>
+      <c r="R24" t="n">
+        <v>631</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1302214665</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302214665</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>옥련헬스</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ssoyoung0318@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 옥련로 33</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>17</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>38362882</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38362882</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>R2B운동과학센터</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>r2besc@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1394-0828</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 15 송도아메리칸타운아이파크 상가 104동 222호~230호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/r2besc</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>657</v>
+      </c>
+      <c r="R26" t="n">
+        <v>688</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>38466567</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38466567</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>제이짐&amp;PT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>herricane@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1389-1029</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 비류대로433번길 11 연수길프라자 3층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/jaygym_yeonsudong</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>69</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>31833454</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31833454</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>070-4594-4423</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 연수동</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1937810626</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1937810626</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>플랜피트니스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>planfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1334-7654</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 독배로40번길 43 신송빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/planfitness_86</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>149</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1426055493</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426055493</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>카이짐동춘점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kaigym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1327-0169</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 앵고개로 260 3층 304~313호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kaigym2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>90</v>
+      </c>
+      <c r="R30" t="n">
+        <v>146</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2079653679</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079653679</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>동춘동스카이휘트니스</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dnlacm@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1423-1144</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로63번길 13 지하1층 스카이휘트니스</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dnlacm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>57</v>
+      </c>
+      <c r="R31" t="n">
+        <v>236</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>35076285</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35076285</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5150피트니스 송도점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5150fitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1485-5150</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로125번길 7 3층 5150피트니스 송도점</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/5150fitness3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1301</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1042</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2343</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1318542021</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1318542021</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>원모어피트니스 송도점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>qkdnf1541@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1376-2361</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로152번길 31 801호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onemorefitness24</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>218</v>
+      </c>
+      <c r="R33" t="n">
+        <v>295</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1783938722</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1783938722</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>매드볼릭 PT 헬스장 송도</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>madbolic-songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1352-6741</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/madbolic-songdo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>576</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1326</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1902</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1206099126</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206099126</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>바디홀릭옥련점 헬스PT&amp;필라테스&amp;요가&amp;스피닝</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>haon8312@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1403-9682</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 청량로 217 3층 기구필라테스 4층 피트니스</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s4LOp7Wh</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>957</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>299</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1256</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>37695643</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37695643</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>커브스 동춘클럽</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>zjqmtm87@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1382-7330</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 앵고개로 260 맘모스프라자 6층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/zjqmtm87</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>268</v>
+      </c>
+      <c r="R36" t="n">
+        <v>347</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>13206949</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13206949</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>헤라클레스짐 PT&amp;헬스 송도점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mee_hwa90@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1325-2728</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 GTX센트럴상가 B동 9층 헤라클레스짐</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://헤라클레스짐송도점.kr/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>732</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1019</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1276642503</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1276642503</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>고다짐 송도점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>godagym_sd@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1391-5466</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 114 지층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.godagym.com</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>272</v>
+      </c>
+      <c r="R38" t="n">
+        <v>385</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1692050159</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692050159</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FLEX GYM</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dengsu3@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 선학로68번길 3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1055153750</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1055153750</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>플렉스짐</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>flexgym_seonhak@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1335-9689</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 선학로68번길 3 연주빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/flex_gym_seonhak/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>724</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>299</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1023</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>37224693</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37224693</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>송도 피크짐 연중무휴 PT 헬스장</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>songdo_pikgym365@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1426-1817</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 229호 230호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/songdo_pikgym365?tab=1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>148</v>
+      </c>
+      <c r="R41" t="n">
+        <v>275</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1110236566</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110236566</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>티와이짐 프리미엄 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>tygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1386-4975</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 독배로 29 윤프라자 6층 티와이짐</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tygym</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>64</v>
+      </c>
+      <c r="R42" t="n">
+        <v>258</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1606327385</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606327385</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>070-8904-7225</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 연수동</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1225871113</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1225871113</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>플라이휘트니스 동춘점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>flyfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1436-5567</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 앵고개로 262 동경프라자 7층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fly_fitness_1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>432</v>
+      </c>
+      <c r="R44" t="n">
+        <v>779</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1573462675</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1573462675</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>070-8904-9016</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 선학동</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1106867169</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106867169</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>올피플 24시 헬스 PT 연수 동춘점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>all_people@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1400-8338</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_gAxafn</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>477</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1253864345</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1253864345</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>짐25 피트니스</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gym25_yeonsu@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1352-0555</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 벚꽃로 114 4층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym25_yeonsu</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>3154</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>170</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3324</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1228611528</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228611528</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>더피티짐 헬스&amp;PT 글로벌캠퍼스점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>kyu0000000@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1320-3080</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도문화로28번길 28 글로벌캠퍼스푸르지오상가 202동 2층 208-210호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://thepit.creatorlink.net</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>705</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1037</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1189916238</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1189916238</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>더피티짐 헬스&amp;PT 리치센트럴점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>awake8372@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1465-9304</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 8층 810~811호 더피티짐</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://thepit.creatorlink.net</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1403</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1752</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1362792414</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1362792414</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>YC바디핏</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ycbodyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1324-3669</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 독배로 56 2층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ycbodyfit</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>27</v>
+      </c>
+      <c r="R50" t="n">
+        <v>73</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1806361377</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806361377</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>퍼스트짐 PT&amp;헬스 송도점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>tynsongdo12@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1497-9061</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 3층 311~314호 퍼스트짐 송도점</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_firstgym_songdo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>514</v>
+      </c>
+      <c r="R51" t="n">
+        <v>702</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1140180251</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140180251</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>클래식더짐 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>happy3747@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1368-4594</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로125번길 7 이리옴프라자 5층 505호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/happy3747</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>544</v>
+      </c>
+      <c r="R52" t="n">
+        <v>623</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1148859143</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1148859143</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>핏더라운지 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>fitthelounge_@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1339-9679</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로168번길 100 G동 2층 248-250호 핏더라운지</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitthelounge_</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>994</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1359</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1726182684</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726182684</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>무포스 PT FT 송도점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>moveforstrength@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1406-4500</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.moveforstrength.co.kr/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>645</v>
+      </c>
+      <c r="R54" t="n">
+        <v>760</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1426191152</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426191152</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>클린짐 원인재점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>nowonablegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 원인재로 180 우성2차아파트상가 지하1층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nowonablegym</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>169</v>
+      </c>
+      <c r="R55" t="n">
+        <v>319</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1023031065</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1023031065</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>컬쳐드 크로스핏</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>culturedcrossfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1387-2113</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 204 인스타1 지하1층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/culturedcrossfit</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>68</v>
+      </c>
+      <c r="R56" t="n">
+        <v>363</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1667441034</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667441034</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>웨스트짐 PT&amp;필라 동춘점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>westgym_yeob@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1349-9329</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로 92 503호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://westgym.kr/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>169</v>
+      </c>
+      <c r="R57" t="n">
+        <v>314</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1678620909</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1678620909</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>메이드핏 청학점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>madefit1@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>032-258-9696</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 용담로 11 3층 메이드핏</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/madefit1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>70</v>
+      </c>
+      <c r="R58" t="n">
+        <v>278</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1605079411</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1605079411</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠용품</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>연수 올피플 PT 헬스 상담센터</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>all_people@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 용담로 111 6층 6656호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://naver.me/F1ry4EQM</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2034739283</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034739283</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>포텐휘트니스 헬스&amp;PT 선학점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fitness410_@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1324-5075</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 학나래로118번길 9 선학프라자 4층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitness410_</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1049</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>143</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1192</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1898375436</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898375436</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>오빠네피티샵&amp;헬스 연수점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oppagym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1493-9880</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로 190 4층 401호,402호,403호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oppa_gym_pt/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>718</v>
+      </c>
+      <c r="R61" t="n">
+        <v>823</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1366841161</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1366841161</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>솔직한마케팅 인천연수점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>zianear@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1312-6916</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 청량로184번길 17</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/soNtwTci</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1397901299</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397901299</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>구민체육센터</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>옹암체육센터</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>chldms30@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>032-830-8312</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 비류대로 142 옹암체육센터</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://ongam.ysfsmc.or.kr/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>20</v>
+      </c>
+      <c r="R63" t="n">
+        <v>40</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1630450734</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1630450734</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>리버스바디</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>reverse-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1414-6778</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 3층 302, 303호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/reverse-gym</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>384</v>
+      </c>
+      <c r="R64" t="n">
+        <v>575</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>37928664</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37928664</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>리젠핏 스튜디오 PT 송도점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>regenfitstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1437-1950</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로152번길 35 퍼스트프라자 604호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/regenfit_official/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>665</v>
+      </c>
+      <c r="R65" t="n">
+        <v>822</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1874099957</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874099957</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>피지컬랩 송도PT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>maxyh7@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1332-2194</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고 타워 502호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/maxyh7/222056811037</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>543</v>
+      </c>
+      <c r="R66" t="n">
+        <v>731</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1826127652</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1826127652</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 더테라스점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gktk1877@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1307-1061</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://theptgym.clickn.co.kr/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>663</v>
+      </c>
+      <c r="R67" t="n">
+        <v>709</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1296216271</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296216271</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>애프터핏</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>afterfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1391-5968</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 앵고개로264번길 46 동춘빌딩 3층 애프터핏</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/afterfit</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>89</v>
+      </c>
+      <c r="R68" t="n">
+        <v>166</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1710714991</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1710714991</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>바디첵 스포츠재활운동센터</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bodycheck1@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1302-8311</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 용담로 111 5층 바디첵스포츠재활운동센터.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodycheck1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>196</v>
+      </c>
+      <c r="R69" t="n">
+        <v>240</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>35830369</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35830369</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>헨리스짐</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>redgoldmy@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 캠퍼스타운 상가 B동 2층 215호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ok_top_henry</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>6</v>
+      </c>
+      <c r="R70" t="n">
+        <v>17</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1584713546</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1584713546</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>팀바디첵</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1360-9731</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 용담로 111 5층 509호 (연수동, 아시스타워)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R71" t="n">
+        <v>3</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1315006645</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1315006645</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>여성전용PT 핏투핏 송도점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>waterfallbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1458-9510</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 87 401동 2층 210호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/waterfallbody</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>826</v>
+      </c>
+      <c r="R72" t="n">
+        <v>963</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1851119903</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1851119903</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>치프 스포츠 트레이닝 재활PT센터</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jayayy88@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1475-0952</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 101동 507호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jayayy88</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>37</v>
+      </c>
+      <c r="R73" t="n">
+        <v>45</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1668102513</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1668102513</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>송도 리엠PT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>fldpavlxl22@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1306-9102</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 168-7 레드원프라자 6층 603호 리엠PT</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fldpavlxl22</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>497</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>896</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1393</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1533793344</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1533793344</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>건강찬피티</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pcw7181@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1307-1190</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 봉재산로36번길 1 3층 304호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chan_personaltraining/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>76</v>
+      </c>
+      <c r="R75" t="n">
+        <v>88</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1095769375</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1095769375</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>환스튜디오PT 송도점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hwansstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1436-1273</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로16번길 13-39 1층 환스튜디오</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hwansstudio</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>922</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1190</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1260247315</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260247315</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>라이크짐 송도</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>kybayo112@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1346-9492</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 첨단대로 80 레지던스 라이크홈 2층 208호 라이크짐</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/likegym_songdo/</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>23</v>
+      </c>
+      <c r="R77" t="n">
+        <v>106</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1379614052</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379614052</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>하이어짐PT 송도점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>highsongdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1474-8260</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/highsongdo</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1317</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1487</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1642474825</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1642474825</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>피플운동센터 재활&amp;PT 송도타임스페이스점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>physioplace-@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1491-0647</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도 타임스페이스 B동 904호</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>http://www.physioplace.co.kr</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>302</v>
+      </c>
+      <c r="R79" t="n">
+        <v>351</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1097730397</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1097730397</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>팀윤짐 PT 송도7호점</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>teamyoon_7@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1487-9688</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamyoon_7</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>567</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1309</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1876</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1876943780</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1876943780</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>룩바디짐 PT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>lukbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1462-2244</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 101동 401호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lukbody</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>338</v>
+      </c>
+      <c r="R81" t="n">
+        <v>638</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1909769673</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1909769673</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>스타크짐 PT 송도본점</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>starkgym_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1433-7781</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로132번길 30 휴먼빌파크 6층 스타크짐 퍼스널 트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_UevaG</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>567</v>
+      </c>
+      <c r="R82" t="n">
+        <v>712</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1487669358</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487669358</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>팀윤짐 PT 송도4호점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>teamyoonsongdo3@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1315-9683</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 160 A동 2층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://teamyoongym.com/440</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1099</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1524</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1338590785</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338590785</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>physiostudio_7@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1356-5739</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/physiostudio_7</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>549</v>
+      </c>
+      <c r="R84" t="n">
+        <v>602</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2019067639</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019067639</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>아인스멀티짐 송도점</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>einsmultigym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1405-4501</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 166 플러스원 프라자 5층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/einsmultigym_</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1445</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1647</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>35352221</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35352221</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>이지핏</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>cyranox@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1387-5768</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 독배로40번길 21 유한빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cyranox</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>254</v>
+      </c>
+      <c r="R86" t="n">
+        <v>332</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1101068759</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101068759</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 학원가점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>qoqofh677@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1446-9681</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://theptgym.clickn.co.kr/</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1933</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1063156519</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1063156519</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>아리스 휘트니스 퓨어</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>aris_songdo_pure@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1388-9683</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-14 8, 9층 전체</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aris_fitness_pure</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>118</v>
+      </c>
+      <c r="R88" t="n">
+        <v>272</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2033238108</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2033238108</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>솔루션피트니스</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>solution_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1392-2038</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 c동 346~354</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/solution_fitness</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>460</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>319</v>
+      </c>
+      <c r="R89" t="n">
+        <v>779</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1392113756</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1392113756</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>팀비스트짐 PT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>team_beast@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1368-8303</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 102 4층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/team_beast</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>1011</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>593</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1604</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1349969899</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349969899</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>베니스짐 옥련점 PT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>venice_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1458-8087</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 독배로40번길 11 효명프라자 지하층 101호</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/venice_pt/</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>214</v>
+      </c>
+      <c r="R91" t="n">
+        <v>449</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1040646798</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040646798</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>바디채널 동춘점</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>rys0924@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1416-5760</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로 88 상산빌딩 6층 바디채널 동춘점</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodychannel_dongchun/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>447</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2329</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2776</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1589960475</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1589960475</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>코어앤모어 PT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>coreandmore@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1319-5328</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
         <v>80</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q93" t="n">
         <v>111</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R93" t="n">
         <v>191</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
         <is>
           <t>2021439008</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2021439008</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>from-body@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1425-0923</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://frombody.kr</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1589</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1880</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1472986584</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1472986584</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>준토스핏PT 송도 트리플점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>juntosfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1304-4383</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로28번길 8 207호 준토스핏</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/juntosfit</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1584</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1741</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1859724879</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1859724879</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>메이드핏바이브래이디</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>redgoldmy@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1470-3049</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도미래로11번길 27 A동 310호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/madefit_by_brady</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>9</v>
+      </c>
+      <c r="R96" t="n">
+        <v>23</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1176352806</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176352806</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>필로스짐</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>pilos_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>032-812-3533</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 새말로96번길 26 2층 201호</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilos_gym</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>23</v>
+      </c>
+      <c r="R97" t="n">
+        <v>76</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1168977029</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1168977029</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>라이노스트렝스</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>yjh000127@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1437-1566</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 먼우금로 282 상가동 2층 205호</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rhinostrength_kor/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1036288584</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036288584</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>송도PT 볼드짐</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>boldgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1388-8284</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 D동 304, 305호</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/boldgym2</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>43</v>
+      </c>
+      <c r="R99" t="n">
+        <v>120</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1509661314</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1509661314</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>샤머니짐 송도점</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>shamanigym_songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1330-9030</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shamanigym/</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>1387</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>933</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2320</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1040543457</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040543457</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>크로스핏 케이핏포스 연수점</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 동곡재로 46 3호 크로스핏 케이핏포스 연수점</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/kfitforce</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>626</v>
+      </c>
+      <c r="R101" t="n">
+        <v>692</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1215733573</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1215733573</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>송도PT 준토스핏 프리미엄점</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>juntosfitpremium@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1443-1973</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로130번길 20 6층 602~4호</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.juntosfitpremium.com</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>251</v>
+      </c>
+      <c r="R102" t="n">
+        <v>295</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>2020902408</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020902408</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>준피티</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>june-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1400-7330</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 원인재로 14 상가동 3층 310호</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/june-pt</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>115</v>
+      </c>
+      <c r="R103" t="n">
+        <v>216</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1568147703</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1568147703</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>원스트렝스역도짐 연수역점</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0507-1334-7360</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 함박뫼로50번길 93 지하</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hsi2800s?igsh=cmw4NzQ0YXZxZ3dj&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>4</v>
+      </c>
+      <c r="R104" t="n">
+        <v>4</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>2073504271</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2073504271</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/연수구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/연수구_헬스장.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>머슬몽키짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessinssongdo@naver.com</t>
+          <t>coke3183@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1407-9979</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://www.instagram.com/muscle_monkey_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,18 +601,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4btcu</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1578</v>
+        <v>235</v>
       </c>
       <c r="Q2" t="n">
-        <v>731</v>
+        <v>147</v>
       </c>
       <c r="R2" t="n">
-        <v>2309</v>
+        <v>382</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>38234040</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/38234040</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>연수동PT 하이엔드 연수점</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>highendfit@naver.com</t>
+          <t>fitnessinssongdo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1466-3414</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.highendfitness.kr/default/</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>699</v>
+        <v>1581</v>
       </c>
       <c r="Q3" t="n">
-        <v>308</v>
+        <v>732</v>
       </c>
       <c r="R3" t="n">
-        <v>1007</v>
+        <v>2313</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1725784787</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725784787</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>올피플 24시 헬스 PT 연수 동춘점</t>
+          <t>연수동PT 하이엔드 연수점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>all_people@naver.com</t>
+          <t>highendfit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1400-8338</t>
+          <t>0507-1466-3414</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
+          <t>인천광역시 연수구 청능대로 93 연수동 이리옴프라자 7층 하이엔드 연수점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gAxafn</t>
+          <t>http://www.highendfitness.kr/default/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>477</v>
+        <v>705</v>
       </c>
       <c r="Q4" t="n">
-        <v>1195</v>
+        <v>309</v>
       </c>
       <c r="R4" t="n">
-        <v>1672</v>
+        <v>1014</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1253864345</t>
+          <t>1725784787</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253864345</t>
+          <t>https://m.place.naver.com/place/1725784787</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>카이짐동춘점 헬스PT</t>
+          <t>올피플 24시 헬스 PT 연수 동춘점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kaigym2@naver.com</t>
+          <t>all_people@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1327-0169</t>
+          <t>0507-1400-8338</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로 260 3층 304~313호</t>
+          <t>인천광역시 연수구 먼우금로 197 이리옴프라자2 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kaigym2</t>
+          <t>http://pf.kakao.com/_gAxafn</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,22 +898,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56</v>
+        <v>477</v>
       </c>
       <c r="Q5" t="n">
-        <v>90</v>
+        <v>1196</v>
       </c>
       <c r="R5" t="n">
-        <v>146</v>
+        <v>1673</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2079653679</t>
+          <t>1253864345</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079653679</t>
+          <t>https://m.place.naver.com/place/1253864345</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>영스짐 헬스&amp;PT&amp;GX 옥련점</t>
+          <t>카이짐동춘점 헬스PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>young-gym-oy@naver.com</t>
+          <t>kaigym2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1369-4733</t>
+          <t>0507-1327-0169</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 독배로 35 601, 602호</t>
+          <t>인천 연수구 앵고개로 260 3층 304~313호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/young-gym-oy</t>
+          <t>https://blog.naver.com/kaigym2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,10 +986,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wolq2d4</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="R6" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2030292479</t>
+          <t>2079653679</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030292479</t>
+          <t>https://m.place.naver.com/place/2079653679</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머슬몽키짐</t>
+          <t>영스짐 헬스&amp;PT&amp;GX 옥련점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>coke3183@naver.com</t>
+          <t>young-gym-oy@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1407-9979</t>
+          <t>0507-1369-4733</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
+          <t>인천 연수구 독배로 35 601, 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muscle_monkey_gym</t>
+          <t>https://blog.naver.com/young-gym-oy</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,15 +1079,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2jhjtl</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,17 +1099,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>234</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="n">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
-        <v>381</v>
+        <v>93</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38234040</t>
+          <t>2030292479</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38234040</t>
+          <t>https://m.place.naver.com/place/2030292479</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="Q8" t="n">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="R8" t="n">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1282,10 +1294,10 @@
         <v>317</v>
       </c>
       <c r="Q9" t="n">
-        <v>1934</v>
+        <v>1938</v>
       </c>
       <c r="R9" t="n">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,7 +1316,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1345,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+          <t>인천 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1358,10 +1370,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5icxb</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1376,10 +1392,10 @@
         <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="R10" t="n">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1414,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
